--- a/data/tier_app/tier_app_params.xlsx
+++ b/data/tier_app/tier_app_params.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D39E7C3-1941-C642-A582-EB85ED1B79D9}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D21C08-D635-0343-AE29-2515EAC4D21D}"/>
   <bookViews>
     <workbookView xWindow="-30780" yWindow="-5300" windowWidth="27640" windowHeight="15520" activeTab="1" xr2:uid="{BFD43C4F-988C-0F4F-AE69-989101776492}"/>
   </bookViews>
   <sheets>
     <sheet name="param_list_and_type" sheetId="2" r:id="rId1"/>
-    <sheet name="params_effect" sheetId="1" r:id="rId2"/>
-    <sheet name="params_cost" sheetId="3" r:id="rId3"/>
+    <sheet name="baseline_data" sheetId="4" r:id="rId2"/>
+    <sheet name="params_effect" sheetId="1" r:id="rId3"/>
+    <sheet name="params_cost" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">params_effect!$A$1:$I$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">params_effect!$A$1:$J$205</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="127">
   <si>
     <t>X</t>
   </si>
@@ -360,6 +361,90 @@
   </si>
   <si>
     <t>effect_value</t>
+  </si>
+  <si>
+    <t>coverage</t>
+  </si>
+  <si>
+    <t>absolute</t>
+  </si>
+  <si>
+    <t>absolute (number of calls)? Not sure</t>
+  </si>
+  <si>
+    <t>absolute?</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>PLHIV</t>
+  </si>
+  <si>
+    <t># Diagnosed</t>
+  </si>
+  <si>
+    <t># On ART</t>
+  </si>
+  <si>
+    <t>#Virally Suppressed</t>
+  </si>
+  <si>
+    <t>HIV/TB coinfection rate</t>
+  </si>
+  <si>
+    <t>HIV/cryptococcal co-infection rate</t>
+  </si>
+  <si>
+    <t>#Adult infections</t>
+  </si>
+  <si>
+    <t>#Infant infections</t>
+  </si>
+  <si>
+    <t>#HIV related deaths</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Annual outcomes</t>
+  </si>
+  <si>
+    <t>Population denoms</t>
+  </si>
+  <si>
+    <t>Adult population reached by services</t>
+  </si>
+  <si>
+    <t>Pregnant population</t>
+  </si>
+  <si>
+    <t>Infant population</t>
+  </si>
+  <si>
+    <t>Epidemic params</t>
+  </si>
+  <si>
+    <t>Population receiving prep</t>
+  </si>
+  <si>
+    <t>Proportion AHD</t>
+  </si>
+  <si>
+    <t>Something like tloss to follow-up?</t>
+  </si>
+  <si>
+    <t>Shouold everyone get psychosocial counselling - not everyone may need so would only impact a proprtion of the pop but I am unsure what that denominator would be</t>
+  </si>
+  <si>
+    <t>Some value around those at risk of failure and in need of adherence (althohgh this could be all those not virally suppressed)</t>
+  </si>
+  <si>
+    <t>MMD availability (1 month/ 3 month/6 month)</t>
+  </si>
+  <si>
+    <t>Something about the number of individuals eligible for DSD?</t>
   </si>
 </sst>
 </file>
@@ -400,7 +485,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +495,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -434,6 +525,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -774,6 +868,7 @@
     <col min="1" max="1" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="37" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -824,6 +919,9 @@
       <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="E2" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F2" s="4" t="s">
         <v>0</v>
       </c>
@@ -850,6 +948,9 @@
       <c r="D3" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F3" s="4" t="s">
         <v>0</v>
       </c>
@@ -873,6 +974,9 @@
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="E4" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F4" s="4" t="s">
         <v>0</v>
       </c>
@@ -896,6 +1000,9 @@
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="K5" s="4" t="s">
         <v>0</v>
       </c>
@@ -913,6 +1020,9 @@
       <c r="D6" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="F6" s="4" t="s">
         <v>0</v>
       </c>
@@ -942,6 +1052,9 @@
       <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>0</v>
       </c>
@@ -959,6 +1072,9 @@
       <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="E8" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>0</v>
       </c>
@@ -976,6 +1092,9 @@
       <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="E9" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K9" s="4" t="s">
         <v>0</v>
       </c>
@@ -993,6 +1112,9 @@
       <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="E10" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="K10" s="4" t="s">
         <v>0</v>
       </c>
@@ -1009,6 +1131,9 @@
       </c>
       <c r="D11" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1031,6 +1156,9 @@
       <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="E12" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="K12" s="4" t="s">
         <v>0</v>
       </c>
@@ -1048,6 +1176,9 @@
       <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="E13" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K13" s="4" t="s">
         <v>0</v>
       </c>
@@ -1065,6 +1196,9 @@
       <c r="D14" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="E14" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K14" s="4" t="s">
         <v>0</v>
       </c>
@@ -1082,6 +1216,9 @@
       <c r="D15" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="E15" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K15" s="4" t="s">
         <v>0</v>
       </c>
@@ -1099,6 +1236,9 @@
       <c r="D16" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="E16" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="K16" s="4" t="s">
         <v>0</v>
       </c>
@@ -1116,6 +1256,9 @@
       <c r="D17" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="E17" s="7" t="s">
+        <v>101</v>
+      </c>
       <c r="I17" s="4" t="s">
         <v>0</v>
       </c>
@@ -1139,6 +1282,9 @@
       <c r="D18" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="E18" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
         <v>0</v>
@@ -1164,6 +1310,9 @@
       <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4" t="s">
         <v>0</v>
@@ -1188,6 +1337,9 @@
       </c>
       <c r="D20" s="3" t="s">
         <v>54</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
@@ -1214,6 +1366,9 @@
       <c r="D21" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="E21" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H21" s="4" t="s">
         <v>0</v>
       </c>
@@ -1237,6 +1392,9 @@
       <c r="D22" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="E22" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H22" t="s">
         <v>0</v>
       </c>
@@ -1257,6 +1415,9 @@
       <c r="D23" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="E23" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="H23" t="s">
         <v>0</v>
       </c>
@@ -1277,6 +1438,9 @@
       <c r="D24" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="E24" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H24" t="s">
         <v>0</v>
       </c>
@@ -1297,6 +1461,9 @@
       <c r="D25" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="E25" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H25" t="s">
         <v>0</v>
       </c>
@@ -1317,6 +1484,9 @@
       <c r="D26" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E26" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="G26" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1504,9 @@
       <c r="D27" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="F27" s="3" t="s">
         <v>0</v>
       </c>
@@ -1352,6 +1524,9 @@
       <c r="D28" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="E28" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="F28" t="s">
         <v>0</v>
       </c>
@@ -1369,6 +1544,9 @@
       <c r="D29" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="E29" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F29" t="s">
         <v>0</v>
       </c>
@@ -1386,6 +1564,9 @@
       <c r="D30" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="E30" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F30" t="s">
         <v>0</v>
       </c>
@@ -1403,6 +1584,9 @@
       <c r="D31" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="E31" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="F31" t="s">
         <v>0</v>
       </c>
@@ -1420,6 +1604,9 @@
       <c r="D32" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="E32" s="7" t="s">
+        <v>102</v>
+      </c>
       <c r="F32" t="s">
         <v>0</v>
       </c>
@@ -1434,6 +1621,9 @@
       <c r="D33" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="E33" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="G33" t="s">
         <v>0</v>
       </c>
@@ -1451,6 +1641,9 @@
       <c r="D34" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="E34" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="H34" t="s">
         <v>0</v>
       </c>
@@ -1467,6 +1660,9 @@
       </c>
       <c r="D35" s="3" t="s">
         <v>90</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
@@ -1711,8 +1907,176 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDA1724-5B29-934D-97A3-4F5620D9530D}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B67A41-5C08-024B-8E12-B539DFD980B2}">
-  <dimension ref="A1:I205"/>
+  <dimension ref="A1:J205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1720,10 +2084,11 @@
     <col min="4" max="4" width="37" style="3" customWidth="1"/>
     <col min="5" max="6" width="18.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="3"/>
+    <col min="8" max="8" width="11.33203125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -1746,7 +2111,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1778,12 +2143,12 @@
 )</f>
         <v>Yes</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -1819,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1854,14 +2219,14 @@
       <c r="G4" s="3">
         <v>0</v>
       </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1894,7 +2259,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -1927,7 +2292,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1960,7 +2325,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1993,7 +2358,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -2029,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -2065,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2098,7 +2463,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -2131,7 +2496,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -2167,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2200,7 +2565,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -2236,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -3394,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>13</v>
       </c>
@@ -3427,7 +3792,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>13</v>
       </c>
@@ -3463,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>13</v>
       </c>
@@ -3499,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>13</v>
       </c>
@@ -3535,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>13</v>
       </c>
@@ -3571,7 +3936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>13</v>
       </c>
@@ -3607,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>13</v>
       </c>
@@ -3640,7 +4005,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>13</v>
       </c>
@@ -3675,8 +4040,9 @@
       <c r="G56" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>13</v>
       </c>
@@ -3711,8 +4077,9 @@
       <c r="G57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>13</v>
       </c>
@@ -3747,8 +4114,9 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>13</v>
       </c>
@@ -3783,8 +4151,9 @@
       <c r="G59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>13</v>
       </c>
@@ -3819,8 +4188,9 @@
       <c r="G60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>13</v>
       </c>
@@ -3853,7 +4223,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>13</v>
       </c>
@@ -3889,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>13</v>
       </c>
@@ -3925,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>13</v>
       </c>
@@ -5092,7 +5462,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>13</v>
       </c>
@@ -5125,7 +5495,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>13</v>
       </c>
@@ -5160,8 +5530,9 @@
       <c r="G98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>13</v>
       </c>
@@ -5196,8 +5567,9 @@
       <c r="G99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
@@ -5232,8 +5604,9 @@
       <c r="G100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>13</v>
       </c>
@@ -5266,7 +5639,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="102" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>13</v>
       </c>
@@ -5299,7 +5672,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="103" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>13</v>
       </c>
@@ -5332,7 +5705,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="104" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>13</v>
       </c>
@@ -5367,8 +5740,9 @@
       <c r="G104" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>13</v>
       </c>
@@ -5403,8 +5777,9 @@
       <c r="G105" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>13</v>
       </c>
@@ -5439,8 +5814,9 @@
       <c r="G106" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H106" s="3"/>
+    </row>
+    <row r="107" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>13</v>
       </c>
@@ -5473,7 +5849,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>13</v>
       </c>
@@ -5506,7 +5882,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="109" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>13</v>
       </c>
@@ -5539,7 +5915,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>13</v>
       </c>
@@ -5575,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>13</v>
       </c>
@@ -5611,7 +5987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>13</v>
       </c>
@@ -5647,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>13</v>
       </c>
@@ -5680,7 +6056,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>13</v>
       </c>
@@ -5713,7 +6089,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>13</v>
       </c>
@@ -5746,7 +6122,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>2</v>
       </c>
@@ -5782,7 +6158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>2</v>
       </c>
@@ -5818,7 +6194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>2</v>
       </c>
@@ -5851,7 +6227,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>2</v>
       </c>
@@ -5884,7 +6260,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>2</v>
       </c>
@@ -5920,7 +6296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>2</v>
       </c>
@@ -5956,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>2</v>
       </c>
@@ -5992,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>2</v>
       </c>
@@ -6028,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6437,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>2</v>
       </c>
@@ -6094,7 +6470,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>2</v>
       </c>
@@ -6130,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>2</v>
       </c>
@@ -6166,7 +6542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>2</v>
       </c>
@@ -6201,8 +6577,9 @@
       <c r="G128" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>2</v>
       </c>
@@ -6237,8 +6614,9 @@
       <c r="G129" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>2</v>
       </c>
@@ -6271,7 +6649,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="131" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>2</v>
       </c>
@@ -6304,7 +6682,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="132" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>2</v>
       </c>
@@ -6339,8 +6717,9 @@
       <c r="G132" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>2</v>
       </c>
@@ -6375,8 +6754,9 @@
       <c r="G133" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>2</v>
       </c>
@@ -6412,7 +6792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>2</v>
       </c>
@@ -6448,7 +6828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>2</v>
       </c>
@@ -6481,7 +6861,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>2</v>
       </c>
@@ -6514,7 +6894,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>2</v>
       </c>
@@ -6550,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>2</v>
       </c>
@@ -6586,7 +6966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>2</v>
       </c>
@@ -6622,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>2</v>
       </c>
@@ -6658,7 +7038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>2</v>
       </c>
@@ -6691,7 +7071,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>2</v>
       </c>
@@ -6724,7 +7104,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>2</v>
       </c>
@@ -8446,7 +8826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
         <v>87</v>
       </c>
@@ -8479,7 +8859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>87</v>
       </c>
@@ -8512,7 +8892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>87</v>
       </c>
@@ -8545,7 +8925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>87</v>
       </c>
@@ -8575,7 +8955,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>87</v>
       </c>
@@ -8608,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
         <v>87</v>
       </c>
@@ -8638,7 +9018,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>87</v>
       </c>
@@ -8671,7 +9051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>87</v>
       </c>
@@ -8703,8 +9083,9 @@
       <c r="G200" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H200" s="3"/>
+    </row>
+    <row r="201" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>87</v>
       </c>
@@ -8734,7 +9115,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="202" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>87</v>
       </c>
@@ -8766,8 +9147,9 @@
       <c r="G202" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H202" s="3"/>
+    </row>
+    <row r="203" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>87</v>
       </c>
@@ -8797,7 +9179,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="204" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>87</v>
       </c>
@@ -8829,8 +9211,9 @@
       <c r="G204" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H204" s="3"/>
+    </row>
+    <row r="205" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>87</v>
       </c>
@@ -8862,6 +9245,7 @@
       <c r="G205" s="3">
         <v>0</v>
       </c>
+      <c r="H205" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -8869,7 +9253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C1EB35-7EE8-BE4D-9B8E-69F9F2C4B9B0}">
   <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/data/tier_app/tier_app_params.xlsx
+++ b/data/tier_app/tier_app_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D21C08-D635-0343-AE29-2515EAC4D21D}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D774F40-BA75-724D-91EE-1C883C4A209F}"/>
   <bookViews>
-    <workbookView xWindow="-30780" yWindow="-5300" windowWidth="27640" windowHeight="15520" activeTab="1" xr2:uid="{BFD43C4F-988C-0F4F-AE69-989101776492}"/>
+    <workbookView xWindow="-30780" yWindow="-5300" windowWidth="27640" windowHeight="15520" activeTab="3" xr2:uid="{BFD43C4F-988C-0F4F-AE69-989101776492}"/>
   </bookViews>
   <sheets>
     <sheet name="param_list_and_type" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="129">
   <si>
     <t>X</t>
   </si>
@@ -445,6 +445,12 @@
   </si>
   <si>
     <t>Something about the number of individuals eligible for DSD?</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>unit_cost</t>
   </si>
 </sst>
 </file>
@@ -2110,6 +2116,9 @@
       <c r="G1" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -9255,7 +9264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C1EB35-7EE8-BE4D-9B8E-69F9F2C4B9B0}">
-  <dimension ref="A1:D206"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -9263,7 +9272,7 @@
     <col min="4" max="4" width="37" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -9276,8 +9285,14 @@
       <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -9291,7 +9306,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -9305,7 +9320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -9319,7 +9334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -9333,7 +9348,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -9347,7 +9362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -9361,7 +9376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -9375,7 +9390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -9389,7 +9404,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -9403,7 +9418,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -9417,7 +9432,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -9431,7 +9446,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -9445,7 +9460,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -9459,7 +9474,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -9473,7 +9488,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>

--- a/data/tier_app/tier_app_params.xlsx
+++ b/data/tier_app/tier_app_params.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ae90f5cbd0fd171/AMC/HIV Prioritization tool/HIV_prioritization_tool/data/tier_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D386A8D2-4993-0649-9C64-561A1E0CEB5F}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="8_{3983ECF5-E0D1-344B-BC04-D4E6CF5CD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D14EEC3-3143-8A41-A247-992F22562BDD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="540" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{BFD43C4F-988C-0F4F-AE69-989101776492}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="2" xr2:uid="{BFD43C4F-988C-0F4F-AE69-989101776492}"/>
   </bookViews>
   <sheets>
     <sheet name="param_list_and_type" sheetId="2" r:id="rId1"/>
     <sheet name="tier_plus_updated" sheetId="6" r:id="rId2"/>
-    <sheet name="baseline_data" sheetId="4" r:id="rId3"/>
-    <sheet name="params_effect" sheetId="1" r:id="rId4"/>
-    <sheet name="other_key_values" sheetId="5" r:id="rId5"/>
-    <sheet name="params_cost" sheetId="3" r:id="rId6"/>
+    <sheet name="tier_plus_30Jan" sheetId="7" r:id="rId3"/>
+    <sheet name="baseline_data" sheetId="4" r:id="rId4"/>
+    <sheet name="params_effect" sheetId="1" r:id="rId5"/>
+    <sheet name="other_key_values" sheetId="5" r:id="rId6"/>
+    <sheet name="params_cost" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">params_effect!$A$1:$L$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">params_effect!$A$1:$L$205</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="204">
   <si>
     <t>area</t>
   </si>
@@ -626,6 +627,60 @@
   </si>
   <si>
     <t>https://bushare-my.sharepoint.com/:x:/g/personal/brooken_bu_edu/IQCrAqcnpglYQbFHxzN39mrIAddSipC0bePCNG6CgXoCMBk?e=5xvACO</t>
+  </si>
+  <si>
+    <t>Cotrimoxazole prophylaxis (according to guidelines)</t>
+  </si>
+  <si>
+    <t>tb_test_treat</t>
+  </si>
+  <si>
+    <t>TB Screening and Treatment</t>
+  </si>
+  <si>
+    <t>tpt</t>
+  </si>
+  <si>
+    <t>TPT provision</t>
+  </si>
+  <si>
+    <t>AHD testing and prophylaxis package (LAM, CrAG, CD4, fluconazole)</t>
+  </si>
+  <si>
+    <t>cags</t>
+  </si>
+  <si>
+    <t>Community ART Groups</t>
+  </si>
+  <si>
+    <t>Testing: facility-based (general)</t>
+  </si>
+  <si>
+    <t>Testing: facility-based (targeted)</t>
+  </si>
+  <si>
+    <t>Testing: Network/Index</t>
+  </si>
+  <si>
+    <t>PNC</t>
+  </si>
+  <si>
+    <t>pnc_hiv_test</t>
+  </si>
+  <si>
+    <t>PNC: HIV testing</t>
+  </si>
+  <si>
+    <t>pnc_vl_testing</t>
+  </si>
+  <si>
+    <t>PNC: Viral Load Testing</t>
+  </si>
+  <si>
+    <t>pnc_art_cont</t>
+  </si>
+  <si>
+    <t>PNC: ART continuation</t>
   </si>
 </sst>
 </file>
@@ -733,7 +788,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -773,6 +828,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2841,6 +2899,874 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4335FE8B-B359-CC48-8F11-F322EA2E822B}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDA1724-5B29-934D-97A3-4F5620D9530D}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3032,7 +3958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B67A41-5C08-024B-8E12-B539DFD980B2}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L205"/>
@@ -10452,7 +11378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE40B620-F4DF-C944-9DE6-37E48F558719}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -10518,7 +11444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C1EB35-7EE8-BE4D-9B8E-69F9F2C4B9B0}">
   <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
